--- a/docs/testcase.xlsx
+++ b/docs/testcase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ltmb20260008/work/dog/k6-scenario-test/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79C6174-4A4C-964F-8078-2225B8F1DE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396F5349-4868-4247-A802-3C14185E0046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="25440" windowHeight="17220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -714,33 +714,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>送付メール本文ドラフト表示・申込書</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>PDF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>表示画面を少数ユーザーで操作し、応答時間を計測する</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t>性能基準</t>
     </r>
     <r>
@@ -830,9 +803,6 @@
     <t>G-01</t>
   </si>
   <si>
-    <t>scg010101</t>
-  </si>
-  <si>
     <t>引継書アップロード画面を少数ユーザーで表示し、応答時間を計測する</t>
   </si>
   <si>
@@ -919,9 +889,6 @@
     <t>経験知マスタ候補確認・修正画面の応答時間確認</t>
   </si>
   <si>
-    <t>scg010301</t>
-  </si>
-  <si>
     <t>引継書アップロード後の経験知マスタ候補確認・修正画面を少数ユーザーで操作し、応答時間を計測する</t>
   </si>
   <si>
@@ -3707,6 +3674,37 @@
   </si>
   <si>
     <t>確認メール本文ドラフト表示画面 (scb040101?applicationId=9&amp;missing_field_ids=120) を少数ユーザーで操作し、応答時間を計測する</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <r>
+      <t>送付メール本文ドラフト表示・申込書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>PDF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>表示画面を少数ユーザーで操作し、応答時間を計測する</t>
+    </r>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>scg010101</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>scg010301</t>
     <phoneticPr fontId="19"/>
   </si>
 </sst>
@@ -4067,11 +4065,11 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4274,16 +4272,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1405647</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>574375</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>538562</xdr:rowOff>
+      <xdr:rowOff>630925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>90801</xdr:colOff>
+      <xdr:colOff>3935438</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>58751</xdr:rowOff>
+      <xdr:rowOff>151114</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4298,7 +4296,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3345283" y="4706471"/>
+          <a:off x="7189920" y="4798834"/>
           <a:ext cx="3361063" cy="1806189"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
@@ -4405,16 +4403,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>32487</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>758657</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>575124</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>54385</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2557703</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3100340</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>630290</xdr:rowOff>
+      <xdr:rowOff>688018</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4429,8 +4427,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3476881" y="7233733"/>
-          <a:ext cx="2525216" cy="631709"/>
+          <a:off x="7190669" y="7270294"/>
+          <a:ext cx="2525216" cy="633633"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
@@ -4534,15 +4532,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>32487</xdr:colOff>
+      <xdr:colOff>2179942</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>75551</xdr:rowOff>
+      <xdr:rowOff>237187</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2557703</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>707260</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1541704</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>106896</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4557,7 +4555,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3476881" y="8070778"/>
+          <a:off x="5632033" y="8215096"/>
           <a:ext cx="2525216" cy="631709"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
@@ -4993,7 +4991,7 @@
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" s="7" customFormat="1" ht="60" customHeight="1">
-      <c r="B6" s="26">
+      <c r="B6" s="25">
         <f t="shared" ref="B6:B22" si="0">ROW()-5</f>
         <v>1</v>
       </c>
@@ -5004,7 +5002,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>18</v>
@@ -5024,7 +5022,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="60" customHeight="1">
-      <c r="B7" s="26">
+      <c r="B7" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -5041,7 +5039,7 @@
         <v>24</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>26</v>
@@ -5055,7 +5053,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" customHeight="1">
-      <c r="B8" s="26">
+      <c r="B8" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -5072,7 +5070,7 @@
         <v>24</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>28</v>
@@ -5086,7 +5084,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="60" customHeight="1">
-      <c r="B9" s="26">
+      <c r="B9" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -5103,21 +5101,21 @@
         <v>30</v>
       </c>
       <c r="G9" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>127</v>
       </c>
       <c r="J9" s="14"/>
       <c r="K9" s="12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60" customHeight="1">
-      <c r="B10" s="26">
+      <c r="B10" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -5134,10 +5132,10 @@
         <v>33</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>21</v>
@@ -5148,7 +5146,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" customHeight="1">
-      <c r="B11" s="26">
+      <c r="B11" s="25">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -5168,7 +5166,7 @@
         <v>37</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>21</v>
@@ -5179,7 +5177,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="60" customHeight="1">
-      <c r="B12" s="11">
+      <c r="B12" s="25">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -5199,18 +5197,18 @@
         <v>41</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="60" customHeight="1">
-      <c r="B13" s="26">
+      <c r="B13" s="25">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -5221,27 +5219,27 @@
         <v>17</v>
       </c>
       <c r="E13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="G13" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="12" t="s">
         <v>45</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>47</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="60" customHeight="1">
-      <c r="B14" s="11">
+      <c r="B14" s="25">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -5252,27 +5250,27 @@
         <v>17</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="60" customHeight="1">
-      <c r="B15" s="26">
+      <c r="B15" s="25">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -5283,27 +5281,27 @@
         <v>17</v>
       </c>
       <c r="E15" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>56</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J15" s="14"/>
       <c r="K15" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="60" customHeight="1">
-      <c r="B16" s="26">
+      <c r="B16" s="25">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -5314,38 +5312,38 @@
         <v>17</v>
       </c>
       <c r="E16" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="12" t="s">
         <v>58</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>61</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J16" s="14"/>
       <c r="K16" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="60" customHeight="1">
-      <c r="B17" s="11">
+      <c r="B17" s="25">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>24</v>
@@ -5354,29 +5352,29 @@
         <v>25</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J17" s="14"/>
       <c r="K17" s="12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="60" customHeight="1">
-      <c r="B18" s="11">
+      <c r="B18" s="25">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>30</v>
@@ -5385,14 +5383,14 @@
         <v>31</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J18" s="14"/>
       <c r="K18" s="12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="60" customHeight="1">
@@ -5401,29 +5399,29 @@
         <v>14</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E19" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="I19" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="60" customHeight="1">
@@ -5432,13 +5430,13 @@
         <v>15</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>40</v>
@@ -5447,14 +5445,14 @@
         <v>41</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="60" customHeight="1">
@@ -5463,29 +5461,29 @@
         <v>16</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>83</v>
       </c>
       <c r="J21" s="14"/>
       <c r="K21" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="60" customHeight="1">
@@ -5494,29 +5492,29 @@
         <v>17</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="60" customHeight="1"/>
@@ -5621,141 +5619,141 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="40.5" customHeight="1">
       <c r="B4" s="17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="67.5" customHeight="1">
       <c r="B5" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="18" customHeight="1">
-      <c r="B7" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="25"/>
+      <c r="B7" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="26"/>
     </row>
     <row r="8" spans="2:3">
       <c r="B8" s="18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="B12" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="B13" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="B14" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="18" customHeight="1">
-      <c r="B16" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="25"/>
+      <c r="B16" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="26"/>
     </row>
     <row r="17" spans="2:3" ht="27" customHeight="1">
       <c r="B17" s="22" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="27" customHeight="1">
       <c r="B18" s="22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="27" customHeight="1">
       <c r="B19" s="22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="22" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="30">
       <c r="B23" s="22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="39.75" customHeight="1">
@@ -5763,7 +5761,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="39.75" customHeight="1">
@@ -5771,7 +5769,7 @@
         <v>9</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -5786,6 +5784,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c58ecc89-2e47-4dee-a93d-93f030b574a9" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65048e3-dffa-4253-8538-8fa05818bc09">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010060506946A466D34388C42452DB951185" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee7d9a8583174e9062ac3cca65451de1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65048e3-dffa-4253-8538-8fa05818bc09" xmlns:ns3="c58ecc89-2e47-4dee-a93d-93f030b574a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="994234e16438a2c0e5867837252958bb" ns2:_="" ns3:_="">
     <xsd:import namespace="b65048e3-dffa-4253-8538-8fa05818bc09"/>
@@ -5986,27 +6004,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33FDF242-3060-4466-8BD1-F5814F4054AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="b65048e3-dffa-4253-8538-8fa05818bc09"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c58ecc89-2e47-4dee-a93d-93f030b574a9"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c58ecc89-2e47-4dee-a93d-93f030b574a9" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65048e3-dffa-4253-8538-8fa05818bc09">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAD3DA1-56D0-41A7-A6DF-01EC2C4DA25A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82C24A4F-C4D0-4310-8910-CAE4F2821C32}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6023,29 +6046,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAD3DA1-56D0-41A7-A6DF-01EC2C4DA25A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33FDF242-3060-4466-8BD1-F5814F4054AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="b65048e3-dffa-4253-8538-8fa05818bc09"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c58ecc89-2e47-4dee-a93d-93f030b574a9"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>